--- a/Demand.xlsx
+++ b/Demand.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ivlse-my.sharepoint.com/personal/erik_emilsson_ivl_se/Documents/Skrivbordet/temp_github/ELiMINATE_EU_MFA/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC1048DBE95E7B845BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A51273-CB7C-4AE9-AA00-341464043ACA}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="34776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -33,312 +22,320 @@
     <t>Country</t>
   </si>
   <si>
+    <t>City</t>
+  </si>
+  <si>
     <t>Latitude</t>
   </si>
   <si>
     <t>Longitude</t>
   </si>
   <si>
-    <t>City</t>
+    <t>Tonnes</t>
   </si>
   <si>
     <t>Freyr Battery (Giga Vaasa)</t>
   </si>
   <si>
+    <t>Verkor</t>
+  </si>
+  <si>
+    <t>ACC (Stellantis/Saft)</t>
+  </si>
+  <si>
+    <t>Envision AESC</t>
+  </si>
+  <si>
+    <t>Customcells</t>
+  </si>
+  <si>
+    <t>CATL</t>
+  </si>
+  <si>
+    <t>Tesla Gigafactory Berlin-Brandenburg</t>
+  </si>
+  <si>
+    <t>Nortvolt Drei</t>
+  </si>
+  <si>
+    <t>SVOLT</t>
+  </si>
+  <si>
+    <t>Microvast</t>
+  </si>
+  <si>
+    <t>Leclanché</t>
+  </si>
+  <si>
+    <t>PowerCo SalzGiga (Volkswagen)</t>
+  </si>
+  <si>
+    <t>BMW</t>
+  </si>
+  <si>
+    <t>Cellforce</t>
+  </si>
+  <si>
+    <t>Blackstone Resources</t>
+  </si>
+  <si>
+    <t>UniverCell</t>
+  </si>
+  <si>
+    <t>SK Innovation</t>
+  </si>
+  <si>
+    <t>Samsung Göd</t>
+  </si>
+  <si>
+    <t>CATL Debrecen</t>
+  </si>
+  <si>
+    <t>Italvolt</t>
+  </si>
+  <si>
+    <t>ACC</t>
+  </si>
+  <si>
+    <t>FAAM</t>
+  </si>
+  <si>
+    <t>Anodox</t>
+  </si>
+  <si>
+    <t>Eurocell</t>
+  </si>
+  <si>
+    <t>Morrow</t>
+  </si>
+  <si>
+    <t>Beyonder</t>
+  </si>
+  <si>
+    <t>Freyr (Mo i Rana)</t>
+  </si>
+  <si>
+    <t>LG Energy Solution</t>
+  </si>
+  <si>
+    <t>CALB</t>
+  </si>
+  <si>
+    <t>ElevenEs</t>
+  </si>
+  <si>
+    <t>Inobat</t>
+  </si>
+  <si>
+    <t>InoBat</t>
+  </si>
+  <si>
+    <t>Gigafactory Valencia: PowerCo (Volkswagen)</t>
+  </si>
+  <si>
+    <t>Phi4tech</t>
+  </si>
+  <si>
+    <t>Basquevolt</t>
+  </si>
+  <si>
+    <t>Northvolt Ett</t>
+  </si>
+  <si>
+    <t>Northvolt–Volvo Cars</t>
+  </si>
+  <si>
+    <t>Rosatom</t>
+  </si>
+  <si>
+    <t>AMTE Power</t>
+  </si>
+  <si>
+    <t>West Midlands</t>
+  </si>
+  <si>
     <t>Finland</t>
   </si>
   <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Vaasa</t>
   </si>
   <si>
-    <t>Verkor</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
     <t>Dunkirk</t>
   </si>
   <si>
-    <t>ACC (Stellantis/Saft)</t>
-  </si>
-  <si>
     <t>Kiserslautern</t>
   </si>
   <si>
-    <t>Envision AESC</t>
-  </si>
-  <si>
     <t>Duoai</t>
   </si>
   <si>
-    <t>Customcells</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
     <t>Itzehoe</t>
   </si>
   <si>
-    <t>CATL</t>
-  </si>
-  <si>
     <t>Erfurt</t>
   </si>
   <si>
-    <t>Tesla Gigafactory Berlin-Brandenburg</t>
-  </si>
-  <si>
     <t>Brandenburg</t>
   </si>
   <si>
-    <t>Nortvolt Drei</t>
-  </si>
-  <si>
     <t>Heide</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>SVOLT</t>
-  </si>
-  <si>
-    <t>Microvast</t>
-  </si>
-  <si>
-    <t>Leclanché</t>
-  </si>
-  <si>
-    <t>Willstätt </t>
-  </si>
-  <si>
-    <t>PowerCo SalzGiga (Volkswagen)</t>
+    <t xml:space="preserve">Willstätt </t>
   </si>
   <si>
     <t>Salzgitter</t>
   </si>
   <si>
-    <t>BMW</t>
-  </si>
-  <si>
-    <t>Straßkirchen </t>
-  </si>
-  <si>
-    <t>Cellforce</t>
+    <t xml:space="preserve">Straßkirchen </t>
   </si>
   <si>
     <t>Tübingen</t>
   </si>
   <si>
-    <t>Blackstone Resources</t>
-  </si>
-  <si>
     <t>Döbeln</t>
   </si>
   <si>
-    <t>UniverCell</t>
-  </si>
-  <si>
     <t>Flintbek</t>
   </si>
   <si>
-    <t>SK Innovation</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>Komárom </t>
-  </si>
-  <si>
-    <t>Samsung Göd</t>
+    <t xml:space="preserve">Komárom </t>
   </si>
   <si>
     <t>Göd</t>
   </si>
   <si>
-    <t>CATL Debrecen</t>
-  </si>
-  <si>
     <t>Debrecen</t>
   </si>
   <si>
-    <t>Italvolt</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
     <t>Piedmont</t>
   </si>
   <si>
-    <t>ACC</t>
-  </si>
-  <si>
-    <t>Termoli </t>
-  </si>
-  <si>
-    <t>FAAM</t>
+    <t xml:space="preserve">Termoli </t>
   </si>
   <si>
     <t>Terevola</t>
   </si>
   <si>
-    <t>Anodox</t>
-  </si>
-  <si>
-    <t>Latvia</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Eurocell</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
     <t>Amsterdam</t>
   </si>
   <si>
-    <t>Morrow</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
     <t>Agder</t>
   </si>
   <si>
-    <t>Beyonder</t>
-  </si>
-  <si>
-    <t>Stavanger </t>
-  </si>
-  <si>
-    <t>Freyr (Mo i Rana)</t>
+    <t xml:space="preserve">Stavanger </t>
   </si>
   <si>
     <t>Mo i Rana</t>
   </si>
   <si>
-    <t>LG Energy Solution</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
     <t>Wrocław</t>
   </si>
   <si>
-    <t>CALB</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
     <t>Port of Sines</t>
   </si>
   <si>
-    <t>ElevenEs</t>
-  </si>
-  <si>
-    <t>Serbia</t>
-  </si>
-  <si>
     <t>Subotica</t>
   </si>
   <si>
-    <t>Inobat</t>
-  </si>
-  <si>
-    <t>InoBat</t>
-  </si>
-  <si>
-    <t>Slovakia</t>
-  </si>
-  <si>
     <t>Bratislava</t>
   </si>
   <si>
-    <t>Gigafactory Valencia: PowerCo (Volkswagen)</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>Sagunto, Valencia</t>
   </si>
   <si>
-    <t>Phi4tech</t>
-  </si>
-  <si>
     <t>Noblejas</t>
   </si>
   <si>
-    <t>Basquevolt</t>
-  </si>
-  <si>
     <t>Vitoria-Gasteiz</t>
   </si>
   <si>
     <t>Navalmoral de la Mata</t>
   </si>
   <si>
-    <t>Northvolt Ett</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
     <t>Skellefteå</t>
   </si>
   <si>
-    <t>Northvolt–Volvo Cars</t>
-  </si>
-  <si>
     <t>Gothenburg</t>
   </si>
   <si>
-    <t>Rosatom</t>
-  </si>
-  <si>
-    <t>Russia</t>
-  </si>
-  <si>
     <t>Kalinigrad</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
     <t>Sunderland</t>
   </si>
   <si>
-    <t>AMTE Power</t>
-  </si>
-  <si>
     <t>Dundee</t>
   </si>
   <si>
-    <t>West Midlands</t>
-  </si>
-  <si>
     <t>Coventry</t>
-  </si>
-  <si>
-    <t>Tonnes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -354,7 +351,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -362,26 +359,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -396,44 +403,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -460,15 +467,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -495,7 +501,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -507,279 +512,303 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>63.102111479999998</v>
+        <v>63.10211148</v>
       </c>
       <c r="E2">
         <v>21.64148423</v>
       </c>
       <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D3">
-        <v>51.029510979999998</v>
+        <v>51.02951098</v>
       </c>
       <c r="E3">
         <v>2.372810694</v>
       </c>
       <c r="F3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4">
+        <v>49.45603248</v>
+      </c>
+      <c r="E4">
+        <v>7.748189332</v>
+      </c>
+      <c r="F4">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>49.456032479999998</v>
-      </c>
-      <c r="E4">
-        <v>7.7481893319999999</v>
-      </c>
-      <c r="F4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>50.35657793</v>
       </c>
       <c r="E5">
-        <v>3.0475999439999999</v>
+        <v>3.047599944</v>
       </c>
       <c r="F5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="D6">
-        <v>53.933373799999998</v>
+        <v>53.9333738</v>
       </c>
       <c r="E6">
-        <v>9.4821687889999993</v>
+        <v>9.482168788999999</v>
       </c>
       <c r="F6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D7">
         <v>51.0244821</v>
@@ -788,238 +817,238 @@
         <v>10.97583348</v>
       </c>
       <c r="F7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>52.42230936</v>
       </c>
       <c r="E8">
-        <v>13.785680989999999</v>
+        <v>13.78568099</v>
       </c>
       <c r="F8">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>54.189654769999997</v>
+        <v>54.18965477</v>
       </c>
       <c r="E9">
-        <v>9.0463232619999996</v>
+        <v>9.046323262</v>
       </c>
       <c r="F9">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D10">
         <v>49.44787547</v>
       </c>
       <c r="E10">
-        <v>7.7041606790000001</v>
+        <v>7.704160679</v>
       </c>
       <c r="F10">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D11">
-        <v>52.350501559999998</v>
+        <v>52.35050156</v>
       </c>
       <c r="E11">
         <v>12.59913339</v>
       </c>
       <c r="F11">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12">
+        <v>52.40161274</v>
+      </c>
+      <c r="E12">
+        <v>12.59063206</v>
+      </c>
+      <c r="F12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12">
-        <v>52.401612739999997</v>
-      </c>
-      <c r="E12">
-        <v>12.590632060000001</v>
-      </c>
-      <c r="F12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D13">
-        <v>48.534993700000001</v>
+        <v>48.5349937</v>
       </c>
       <c r="E13">
-        <v>7.9349033670000004</v>
+        <v>7.934903367</v>
       </c>
       <c r="F13">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D14">
-        <v>52.150298079999999</v>
+        <v>52.15029808</v>
       </c>
       <c r="E14">
         <v>10.35919028</v>
       </c>
       <c r="F14">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="D15">
-        <v>48.791643290000003</v>
+        <v>48.79164329</v>
       </c>
       <c r="E15">
-        <v>12.835157819999999</v>
+        <v>12.83515782</v>
       </c>
       <c r="F15">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16">
+        <v>48.51288653</v>
+      </c>
+      <c r="E16">
+        <v>9.075136951999999</v>
+      </c>
+      <c r="F16">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
-        <v>48.512886530000003</v>
-      </c>
-      <c r="E16">
-        <v>9.0751369519999994</v>
-      </c>
-      <c r="F16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D17">
-        <v>51.110703520000001</v>
+        <v>51.11070352</v>
       </c>
       <c r="E17">
         <v>13.17887359</v>
       </c>
       <c r="F17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D18">
-        <v>54.250471930000003</v>
+        <v>54.25047193</v>
       </c>
       <c r="E18">
-        <v>10.027407269999999</v>
+        <v>10.02740727</v>
       </c>
       <c r="F18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D19">
         <v>47.74305073</v>
@@ -1028,121 +1057,121 @@
         <v>18.11894637</v>
       </c>
       <c r="F19">
-        <v>77.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>386500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D20">
         <v>47.68212956</v>
       </c>
       <c r="E20">
-        <v>19.174167149999999</v>
+        <v>19.17416715</v>
       </c>
       <c r="F20">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D21">
         <v>47.53728246</v>
       </c>
       <c r="E21">
-        <v>21.638207099999999</v>
+        <v>21.6382071</v>
       </c>
       <c r="F21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D22">
-        <v>45.129705059999999</v>
+        <v>45.12970506</v>
       </c>
       <c r="E22">
-        <v>7.6948894220000001</v>
+        <v>7.694889422</v>
       </c>
       <c r="F22">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23">
+        <v>41.9948836</v>
+      </c>
+      <c r="E23">
+        <v>14.98120429</v>
+      </c>
+      <c r="F23">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
         <v>50</v>
       </c>
-      <c r="D23">
-        <v>41.994883600000001</v>
-      </c>
-      <c r="E23">
-        <v>14.981204290000001</v>
-      </c>
-      <c r="F23">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D24">
-        <v>41.010535859999997</v>
+        <v>41.01053586</v>
       </c>
       <c r="E24">
         <v>14.1918837</v>
       </c>
       <c r="F24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D25">
-        <v>56.937689980000002</v>
+        <v>56.93768998</v>
       </c>
       <c r="E25">
         <v>24.12798089</v>
@@ -1151,212 +1180,212 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D26">
-        <v>52.328333299999997</v>
+        <v>52.3283333</v>
       </c>
       <c r="E26">
-        <v>4.9134096129999998</v>
+        <v>4.913409613</v>
       </c>
       <c r="F26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D27">
-        <v>58.473649690000002</v>
+        <v>58.47364969</v>
       </c>
       <c r="E27">
-        <v>8.7438428189999993</v>
+        <v>8.743842818999999</v>
       </c>
       <c r="F27">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D28">
-        <v>58.961607489999999</v>
+        <v>58.96160749</v>
       </c>
       <c r="E28">
         <v>5.727296269</v>
       </c>
       <c r="F28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D29">
-        <v>66.320131270000005</v>
+        <v>66.32013127</v>
       </c>
       <c r="E29">
-        <v>14.170974319999999</v>
+        <v>14.17097432</v>
       </c>
       <c r="F29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D30">
-        <v>51.086091660000001</v>
+        <v>51.08609166</v>
       </c>
       <c r="E30">
-        <v>17.011684460000001</v>
+        <v>17.01168446</v>
       </c>
       <c r="F30">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>575000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D31">
         <v>37.99813176</v>
       </c>
       <c r="E31">
-        <v>-8.7512297080000003</v>
+        <v>-8.751229708</v>
       </c>
       <c r="F31">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D32">
-        <v>46.106570859999998</v>
+        <v>46.10657086</v>
       </c>
       <c r="E32">
-        <v>19.794475299999998</v>
+        <v>19.7944753</v>
       </c>
       <c r="F32">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D33">
-        <v>44.051113739999998</v>
+        <v>44.05111374</v>
       </c>
       <c r="E33">
         <v>20.97014905</v>
       </c>
       <c r="F33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D34">
-        <v>48.308211579999998</v>
+        <v>48.30821158</v>
       </c>
       <c r="E34">
         <v>17.55925319</v>
       </c>
       <c r="F34">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D35">
         <v>39.67643271</v>
       </c>
       <c r="E35">
-        <v>-0.27160054719999999</v>
+        <v>-0.2716005472</v>
       </c>
       <c r="F35">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D36">
         <v>39.96766573</v>
@@ -1365,78 +1394,78 @@
         <v>-3.436823644</v>
       </c>
       <c r="F36">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D37">
         <v>42.92635362</v>
       </c>
       <c r="E37">
-        <v>-2.6442975799999999</v>
+        <v>-2.64429758</v>
       </c>
       <c r="F37">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D38">
-        <v>39.889961370000002</v>
+        <v>39.88996137</v>
       </c>
       <c r="E38">
-        <v>-5.5126595639999998</v>
+        <v>-5.512659564</v>
       </c>
       <c r="F38">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D39">
-        <v>64.753128599999997</v>
+        <v>64.7531286</v>
       </c>
       <c r="E39">
-        <v>20.961575150000002</v>
+        <v>20.96157515</v>
       </c>
       <c r="F39">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D40">
         <v>57.71182349</v>
@@ -1445,87 +1474,87 @@
         <v>11.9316096</v>
       </c>
       <c r="F40">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D41">
-        <v>54.646199590000002</v>
+        <v>54.64619959</v>
       </c>
       <c r="E41">
-        <v>20.545088669999998</v>
+        <v>20.54508867</v>
       </c>
       <c r="F41">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D42">
-        <v>54.906804979999997</v>
+        <v>54.90680498</v>
       </c>
       <c r="E42">
-        <v>-1.3908821600000001</v>
+        <v>-1.39088216</v>
       </c>
       <c r="F42">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D43">
-        <v>56.480302999999999</v>
+        <v>56.480303</v>
       </c>
       <c r="E43">
-        <v>-2.9527259809999999</v>
+        <v>-2.952725981</v>
       </c>
       <c r="F43">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44">
-        <v>52.377769069999999</v>
+        <v>52.37776907</v>
       </c>
       <c r="E44">
-        <v>-1.5004837310000001</v>
+        <v>-1.500483731</v>
       </c>
       <c r="F44">
-        <v>60</v>
+        <v>300000</v>
       </c>
     </row>
   </sheetData>
